--- a/剧情配置/数据库导出_事件与节点.xlsx
+++ b/剧情配置/数据库导出_事件与节点.xlsx
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -755,21 +755,6 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>条件JSON</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>消耗JSON</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>效果JSON</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
           <t>目标中文名</t>
         </is>
       </c>
@@ -801,10 +786,7 @@
       <c r="F2" t="n">
         <v>100</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>事件2</t>
         </is>
@@ -837,10 +819,7 @@
       <c r="F3" t="n">
         <v>100</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>强敌</t>
         </is>
